--- a/input/Redistribution_prefate_TRWPs.xlsx
+++ b/input/Redistribution_prefate_TRWPs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nadsad/Documents/GitHub/marilca-cfs-mps/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAB1B4B-8023-F547-B652-6F4AF1C85807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B608E4F-CA2E-1A45-83E2-3113503A58ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{176BB934-54F5-4471-86BE-95D8C132309E}"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="14740" windowHeight="16980" xr2:uid="{176BB934-54F5-4471-86BE-95D8C132309E}"/>
   </bookViews>
   <sheets>
     <sheet name="TC_archetypes" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -93,12 +93,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-removal from rural runoff in swlaes and ditches</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>removal from rural runoff in swlaes and ditches</t>
         </r>
       </text>
     </comment>
@@ -791,7 +800,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -900,6 +909,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2667,7 +2689,7 @@
       </c>
       <c r="C68" s="35">
         <f t="shared" si="2"/>
-        <v>0.43225283752000004</v>
+        <v>0.24191657432000002</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>99</v>
@@ -2961,7 +2983,7 @@
       </c>
       <c r="C74" s="24">
         <f>SUM(C67:C72)</f>
-        <v>1</v>
+        <v>0.80966373680000014</v>
       </c>
       <c r="K74" t="s">
         <v>61</v>
@@ -3227,7 +3249,7 @@
         <v>0.52584065800000002</v>
       </c>
       <c r="AG82" s="33">
-        <v>0.52584065800000002</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="83" spans="10:33" x14ac:dyDescent="0.2">
